--- a/Assets/StreamingAssets/NumbData.xlsx
+++ b/Assets/StreamingAssets/NumbData.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>重量</t>
   </si>
@@ -43,6 +43,9 @@
   </si>
   <si>
     <t>重力缩放</t>
+  </si>
+  <si>
+    <t>数字转换为重量的缩放倍数</t>
   </si>
 </sst>
 </file>
@@ -973,8 +976,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="1"/>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="27.7" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -998,6 +1004,14 @@
       </c>
       <c r="B3">
         <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/NumbData.xlsx
+++ b/Assets/StreamingAssets/NumbData.xlsx
@@ -1,23 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\XIAOBAI1\CPprogram\unityP\ForestIceFireMan\Assets\StreamingAssets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\ForestIceFireMan\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E5F5A11-6C7E-4343-A54F-7B52AB25E604}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4050" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4050" yWindow="4185" windowWidth="21600" windowHeight="11295"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -50,7 +49,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -365,7 +364,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
@@ -385,7 +384,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.15">
@@ -412,7 +411,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
@@ -423,7 +422,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
